--- a/sectors.xlsx
+++ b/sectors.xlsx
@@ -8,13 +8,16 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\zeyad\Desktop\Quads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7760222D-F4DA-46DC-8BC7-5D65265F61B8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3D8A0F5F-533E-4D72-BBBE-C7C5FDC2B124}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="2232" yWindow="2232" windowWidth="17280" windowHeight="8880" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
+  <definedNames>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$C$1</definedName>
+  </definedNames>
   <calcPr calcId="162913"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
@@ -25,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="26" uniqueCount="26">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="39" uniqueCount="39">
   <si>
     <t>SK</t>
   </si>
@@ -69,9 +72,6 @@
     <t>Real Estate</t>
   </si>
   <si>
-    <t>Financials</t>
-  </si>
-  <si>
     <t>Industrials</t>
   </si>
   <si>
@@ -81,18 +81,12 @@
     <t>Consumer Staples</t>
   </si>
   <si>
-    <t>ConsumerDiscretionary</t>
-  </si>
-  <si>
     <t>Utilities</t>
   </si>
   <si>
     <t>Telecomunication</t>
   </si>
   <si>
-    <t>Healthcare</t>
-  </si>
-  <si>
     <t>symbol</t>
   </si>
   <si>
@@ -103,6 +97,54 @@
   </si>
   <si>
     <t>Market</t>
+  </si>
+  <si>
+    <t>Consumer Discretionary</t>
+  </si>
+  <si>
+    <t>Finance</t>
+  </si>
+  <si>
+    <t>Health Care</t>
+  </si>
+  <si>
+    <t>SPY</t>
+  </si>
+  <si>
+    <t>XLK</t>
+  </si>
+  <si>
+    <t>XLE</t>
+  </si>
+  <si>
+    <t>XLRE</t>
+  </si>
+  <si>
+    <t>XLF</t>
+  </si>
+  <si>
+    <t>XLI</t>
+  </si>
+  <si>
+    <t>XLB</t>
+  </si>
+  <si>
+    <t>XLP</t>
+  </si>
+  <si>
+    <t>XLY</t>
+  </si>
+  <si>
+    <t>XLU</t>
+  </si>
+  <si>
+    <t>XLC</t>
+  </si>
+  <si>
+    <t>XLV</t>
+  </si>
+  <si>
+    <t>etf</t>
   </si>
 </sst>
 </file>
@@ -420,117 +462,162 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:B13"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <dimension ref="A1:C13"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="2" max="2" width="16.28515625" customWidth="1"/>
+    <col min="2" max="2" width="16.33203125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
+        <v>19</v>
+      </c>
+      <c r="B1" t="s">
+        <v>20</v>
+      </c>
+      <c r="C1" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A2" t="s">
+        <v>21</v>
+      </c>
+      <c r="B2" t="s">
         <v>22</v>
       </c>
-      <c r="B1" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A2" t="s">
-        <v>24</v>
-      </c>
-      <c r="B2" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="C2" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="B3" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
+        <v>15</v>
+      </c>
+      <c r="C3" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>2</v>
       </c>
       <c r="B4" t="s">
         <v>12</v>
       </c>
-    </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="C4" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="B5" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
+        <v>24</v>
+      </c>
+      <c r="C5" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="B6" t="s">
         <v>14</v>
       </c>
-    </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="C6" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="B7" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.25">
+        <v>11</v>
+      </c>
+      <c r="C7" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="B8" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.25">
+        <v>18</v>
+      </c>
+      <c r="C8" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="9" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
         <v>6</v>
       </c>
       <c r="B9" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.25">
+        <v>16</v>
+      </c>
+      <c r="C9" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="10" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="B10" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="11" spans="1:2" x14ac:dyDescent="0.25">
+        <v>13</v>
+      </c>
+      <c r="C10" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="11" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
         <v>8</v>
       </c>
       <c r="B11" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="12" spans="1:2" x14ac:dyDescent="0.25">
+        <v>17</v>
+      </c>
+      <c r="C11" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="12" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="B12" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="13" spans="1:2" x14ac:dyDescent="0.25">
+        <v>25</v>
+      </c>
+      <c r="C12" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="13" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="B13" t="s">
-        <v>21</v>
+        <v>23</v>
+      </c>
+      <c r="C13" t="s">
+        <v>34</v>
       </c>
     </row>
   </sheetData>
+  <autoFilter ref="A1:C1" xr:uid="{00000000-0001-0000-0000-000000000000}">
+    <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:C13">
+      <sortCondition ref="A1"/>
+    </sortState>
+  </autoFilter>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>
--- a/sectors.xlsx
+++ b/sectors.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\zeyad\Desktop\Quads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3D8A0F5F-533E-4D72-BBBE-C7C5FDC2B124}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6D81E6B7-3402-4D67-A496-DE891A222A3E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="2232" yWindow="2232" windowWidth="17280" windowHeight="8880" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -84,9 +84,6 @@
     <t>Utilities</t>
   </si>
   <si>
-    <t>Telecomunication</t>
-  </si>
-  <si>
     <t>symbol</t>
   </si>
   <si>
@@ -145,6 +142,9 @@
   </si>
   <si>
     <t>etf</t>
+  </si>
+  <si>
+    <t>Telecommunication</t>
   </si>
 </sst>
 </file>
@@ -470,24 +470,24 @@
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
+        <v>18</v>
+      </c>
+      <c r="B1" t="s">
         <v>19</v>
       </c>
-      <c r="B1" t="s">
-        <v>20</v>
-      </c>
       <c r="C1" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
+        <v>20</v>
+      </c>
+      <c r="B2" t="s">
         <v>21</v>
       </c>
-      <c r="B2" t="s">
-        <v>22</v>
-      </c>
       <c r="C2" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.3">
@@ -498,7 +498,7 @@
         <v>15</v>
       </c>
       <c r="C3" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.3">
@@ -509,7 +509,7 @@
         <v>12</v>
       </c>
       <c r="C4" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.3">
@@ -517,10 +517,10 @@
         <v>3</v>
       </c>
       <c r="B5" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C5" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.3">
@@ -531,7 +531,7 @@
         <v>14</v>
       </c>
       <c r="C6" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.3">
@@ -542,7 +542,7 @@
         <v>11</v>
       </c>
       <c r="C7" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.3">
@@ -550,10 +550,10 @@
         <v>9</v>
       </c>
       <c r="B8" t="s">
-        <v>18</v>
+        <v>38</v>
       </c>
       <c r="C8" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
     </row>
     <row r="9" spans="1:3" x14ac:dyDescent="0.3">
@@ -564,7 +564,7 @@
         <v>16</v>
       </c>
       <c r="C9" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
     </row>
     <row r="10" spans="1:3" x14ac:dyDescent="0.3">
@@ -575,7 +575,7 @@
         <v>13</v>
       </c>
       <c r="C10" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
     </row>
     <row r="11" spans="1:3" x14ac:dyDescent="0.3">
@@ -586,7 +586,7 @@
         <v>17</v>
       </c>
       <c r="C11" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
     </row>
     <row r="12" spans="1:3" x14ac:dyDescent="0.3">
@@ -594,10 +594,10 @@
         <v>10</v>
       </c>
       <c r="B12" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="C12" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
     </row>
     <row r="13" spans="1:3" x14ac:dyDescent="0.3">
@@ -605,10 +605,10 @@
         <v>7</v>
       </c>
       <c r="B13" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="C13" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
     </row>
   </sheetData>

--- a/sectors.xlsx
+++ b/sectors.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\zeyad\Desktop\Quads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6D81E6B7-3402-4D67-A496-DE891A222A3E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BFB301D3-A2B6-48F2-9983-05D6D478C849}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2232" yWindow="2232" windowWidth="17280" windowHeight="8880" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="2928" yWindow="2928" windowWidth="17280" windowHeight="8880" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -144,7 +144,7 @@
     <t>etf</t>
   </si>
   <si>
-    <t>Telecommunication</t>
+    <t>Telecommunications</t>
   </si>
 </sst>
 </file>

--- a/sectors.xlsx
+++ b/sectors.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\zeyad\Desktop\Quads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BFB301D3-A2B6-48F2-9983-05D6D478C849}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{165CF6AD-979F-4190-9117-74196238C875}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2928" yWindow="2928" windowWidth="17280" windowHeight="8880" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
